--- a/data/results/2000tok/classifier_steering_results_nemotron_2000_full_aggregated.xlsx
+++ b/data/results/2000tok/classifier_steering_results_nemotron_2000_full_aggregated.xlsx
@@ -494,7 +494,7 @@
         <v>-0.03589552083885781</v>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         <v>-0.03589553206345612</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -692,7 +692,7 @@
         <v>0.2552131844446852</v>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -758,7 +758,7 @@
         <v>0.3859096566627095</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -824,7 +824,7 @@
         <v>0.09328625084304352</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -1022,7 +1022,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1097,7 +1097,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1247,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -1322,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1420,8 +1420,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>0.03956248245573099</v>
@@ -1450,8 +1452,10 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>2.805625689574208e-05</v>
@@ -1463,7 +1467,7 @@
         <v>-0.03589552083885781</v>
       </c>
       <c r="H3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -1480,8 +1484,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>0.03964188011418351</v>
@@ -1510,8 +1516,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>0.167350873260597</v>
@@ -1540,8 +1548,10 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>2.804503229742825e-05</v>
@@ -1553,7 +1563,7 @@
         <v>-0.03589553206345612</v>
       </c>
       <c r="H6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1570,8 +1580,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>0.1245021025021059</v>
@@ -1600,8 +1612,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>0.3913626129585666</v>
@@ -1630,8 +1644,10 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E9" t="n">
         <v>0.03592357709575355</v>
@@ -1643,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -1660,8 +1676,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="D10" t="b">
-        <v>1</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>0.3337392105229133</v>
@@ -1690,8 +1708,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="D11" t="b">
-        <v>1</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E11" t="n">
         <v>0.6267545905588978</v>
@@ -1720,8 +1740,10 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="D12" t="b">
-        <v>1</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E12" t="n">
         <v>0.2911367615404388</v>
@@ -1733,7 +1755,7 @@
         <v>0.2552131844446852</v>
       </c>
       <c r="H12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1750,8 +1772,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="D13" t="b">
-        <v>1</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>0.4105273420092674</v>
@@ -1780,8 +1804,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="D14" t="b">
-        <v>1</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>0.9667936496554517</v>
@@ -1810,8 +1836,10 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="D15" t="b">
-        <v>1</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E15" t="n">
         <v>0.4218332337584631</v>
@@ -1823,7 +1851,7 @@
         <v>0.3859096566627095</v>
       </c>
       <c r="H15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -1840,8 +1868,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="D16" t="b">
-        <v>1</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E16" t="n">
         <v>0.526279453570482</v>
@@ -1870,8 +1900,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="D17" t="b">
-        <v>1</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E17" t="n">
         <v>0.6865434676970188</v>
@@ -1900,8 +1932,10 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E18" t="n">
         <v>0.1292098279387971</v>
@@ -1913,7 +1947,7 @@
         <v>0.09328625084304352</v>
       </c>
       <c r="H18" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1930,8 +1964,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="D19" t="b">
-        <v>1</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E19" t="n">
         <v>0.04213322243115277</v>
@@ -1998,8 +2034,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>0.3913626129585666</v>
@@ -2019,14 +2057,16 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>0.03592357709575355</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -2040,8 +2080,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>0.3337392105229133</v>
@@ -2097,8 +2139,10 @@
           <t>polynomial</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>61</v>
@@ -2115,11 +2159,13 @@
           <t>separable</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -2133,8 +2179,10 @@
           <t>unhomogenous</t>
         </is>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>119</v>
